--- a/Test_Case.xlsx
+++ b/Test_Case.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Progress\OrangHRM\All_Documnets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0B7D08-9ED7-4303-91F2-6CE33AC85DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8164878F-5EC5-450A-9ED1-B446D5C9C66D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
+    <sheet name="PIM" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Login!$A$1:$P$28</definedName>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="241">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -587,6 +588,222 @@
 2. Enter valid username 
 3. Enter valid password with leading space
 4. Click Login</t>
+  </si>
+  <si>
+    <t>FR-07</t>
+  </si>
+  <si>
+    <t>PIM</t>
+  </si>
+  <si>
+    <t>FR-08</t>
+  </si>
+  <si>
+    <t>FR-09</t>
+  </si>
+  <si>
+    <t>FR-10</t>
+  </si>
+  <si>
+    <t>FR-11</t>
+  </si>
+  <si>
+    <t>FR-12</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Verify PIM menu is displayed</t>
+  </si>
+  <si>
+    <t>Verify that the PIM menu is displayed after successful login.</t>
+  </si>
+  <si>
+    <t>User is logged in successfully.</t>
+  </si>
+  <si>
+    <t>Username: Admin, Password: admin123</t>
+  </si>
+  <si>
+    <t>1. Launch OrangeHRM. 2. Login with valid credentials. 3. Verify the PIM menu is displayed.</t>
+  </si>
+  <si>
+    <t>PIM menu should be displayed successfully.</t>
+  </si>
+  <si>
+    <t>verifyPIMMenuIsDisplayed()</t>
+  </si>
+  <si>
+    <t>Verify navigation to PIM module</t>
+  </si>
+  <si>
+    <t>Verify that the user can navigate to the PIM module by clicking the PIM menu.</t>
+  </si>
+  <si>
+    <t>1. Login. 2. Click the PIM menu.</t>
+  </si>
+  <si>
+    <t>User should be navigated to the Employee List page.</t>
+  </si>
+  <si>
+    <t>verifyclickPIM()</t>
+  </si>
+  <si>
+    <t>Verify Employee List page</t>
+  </si>
+  <si>
+    <t>Verify that the Employee List page is displayed after navigating to the PIM module.</t>
+  </si>
+  <si>
+    <t>User is on the PIM page.</t>
+  </si>
+  <si>
+    <t>Valid Login</t>
+  </si>
+  <si>
+    <t>1. Login. 2. Navigate to PIM. 3. Verify Employee List page is displayed.</t>
+  </si>
+  <si>
+    <t>Employee List page should be displayed successfully.</t>
+  </si>
+  <si>
+    <t>verifyisDisplayedEmployeeList()</t>
+  </si>
+  <si>
+    <t>Verify Employee table</t>
+  </si>
+  <si>
+    <t>Verify that the Employee table is displayed on the Employee List page.</t>
+  </si>
+  <si>
+    <t>User is on the Employee List page.</t>
+  </si>
+  <si>
+    <t>1. Login. 2. Navigate to PIM. 3. Verify Employee table.</t>
+  </si>
+  <si>
+    <t>Employee table should be displayed successfully.</t>
+  </si>
+  <si>
+    <t>verifyEmployeeTableDisplayed()</t>
+  </si>
+  <si>
+    <t>Verify Records Found count</t>
+  </si>
+  <si>
+    <t>Verify that the total number of employee records is displayed.</t>
+  </si>
+  <si>
+    <t>1. Login. 2. Navigate to PIM. 3. Read the Records Found count.</t>
+  </si>
+  <si>
+    <t>Records Found count should be greater than zero.</t>
+  </si>
+  <si>
+    <t>verifyGetRecordsFound()</t>
+  </si>
+  <si>
+    <t>Verify Employee row count</t>
+  </si>
+  <si>
+    <t>Verify that employee records are displayed in the Employee table.</t>
+  </si>
+  <si>
+    <t>1. Login. 2. Navigate to PIM. 3. Count employee rows displayed.</t>
+  </si>
+  <si>
+    <t>Employee table should contain one or more employee records.</t>
+  </si>
+  <si>
+    <t>verifyEmployeeRows()</t>
+  </si>
+  <si>
+    <t>Compare Records Found with Employee rows</t>
+  </si>
+  <si>
+    <t>Verify that the displayed employee row count matches the Records Found count on the current page.</t>
+  </si>
+  <si>
+    <t>1. Login. 2. Navigate to PIM. 3. Get Records Found count. 4. Get Employee row count. 5. Compare both values.</t>
+  </si>
+  <si>
+    <t>Records Found count should match the displayed employee row count.</t>
+  </si>
+  <si>
+    <t>compareEmployeeCountRowCount()</t>
+  </si>
+  <si>
+    <t>Verify pagination navigation</t>
+  </si>
+  <si>
+    <t>Verify that clicking the Next button navigates to the next page of employee records.</t>
+  </si>
+  <si>
+    <t>User is on the Employee List page with multiple pages available.</t>
+  </si>
+  <si>
+    <t>1. Login. 2. Navigate to PIM. 3. Capture first Employee ID. 4. Click Next. 5. Capture first Employee ID on next page.</t>
+  </si>
+  <si>
+    <t>The first Employee ID should change after navigating to the next page.</t>
+  </si>
+  <si>
+    <t>VerifyNavigatePagination()</t>
+  </si>
+  <si>
+    <t>Verify Add Employee</t>
+  </si>
+  <si>
+    <t>Verify that a new employee can be added successfully.</t>
+  </si>
+  <si>
+    <t>First Name: yrty, Middle Name: Getty, Last Name: yry</t>
+  </si>
+  <si>
+    <t>1. Login. 2. Navigate to PIM. 3. Click Add. 4. Enter employee details. 5. Click Save.</t>
+  </si>
+  <si>
+    <t>Application should navigate to the Personal Details page after successfully adding the employee.</t>
+  </si>
+  <si>
+    <t>addEmployee()</t>
+  </si>
+  <si>
+    <t>TC-028</t>
+  </si>
+  <si>
+    <t>TC-029</t>
+  </si>
+  <si>
+    <t>TC-030</t>
+  </si>
+  <si>
+    <t>TC-031</t>
+  </si>
+  <si>
+    <t>TC-032</t>
+  </si>
+  <si>
+    <t>TC-033</t>
+  </si>
+  <si>
+    <t>TC-034</t>
+  </si>
+  <si>
+    <t>TC-035</t>
+  </si>
+  <si>
+    <t>TC-036</t>
+  </si>
+  <si>
+    <t>FR-13</t>
+  </si>
+  <si>
+    <t>FR-14</t>
+  </si>
+  <si>
+    <t>FR-15, FR-16</t>
   </si>
 </sst>
 </file>
@@ -638,13 +855,13 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2160,4 +2377,446 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38FA5FA4-4C32-4F33-8B88-4A07D694E041}">
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.21875" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I2" t="s">
+        <v>182</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>92</v>
+      </c>
+      <c r="P2" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" t="s">
+        <v>187</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I4" t="s">
+        <v>194</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" t="s">
+        <v>92</v>
+      </c>
+      <c r="P4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H5" t="s">
+        <v>199</v>
+      </c>
+      <c r="I5" t="s">
+        <v>200</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" t="s">
+        <v>92</v>
+      </c>
+      <c r="P5" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H6" t="s">
+        <v>204</v>
+      </c>
+      <c r="I6" t="s">
+        <v>205</v>
+      </c>
+      <c r="L6" t="s">
+        <v>92</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E7" t="s">
+        <v>208</v>
+      </c>
+      <c r="F7" t="s">
+        <v>198</v>
+      </c>
+      <c r="G7" t="s">
+        <v>192</v>
+      </c>
+      <c r="H7" t="s">
+        <v>209</v>
+      </c>
+      <c r="I7" t="s">
+        <v>210</v>
+      </c>
+      <c r="L7" t="s">
+        <v>92</v>
+      </c>
+      <c r="M7" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" t="s">
+        <v>198</v>
+      </c>
+      <c r="G8" t="s">
+        <v>192</v>
+      </c>
+      <c r="H8" t="s">
+        <v>214</v>
+      </c>
+      <c r="I8" t="s">
+        <v>215</v>
+      </c>
+      <c r="L8" t="s">
+        <v>92</v>
+      </c>
+      <c r="M8" t="s">
+        <v>92</v>
+      </c>
+      <c r="P8" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H9" t="s">
+        <v>220</v>
+      </c>
+      <c r="I9" t="s">
+        <v>221</v>
+      </c>
+      <c r="L9" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" t="s">
+        <v>92</v>
+      </c>
+      <c r="P9" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" t="s">
+        <v>223</v>
+      </c>
+      <c r="E10" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" t="s">
+        <v>191</v>
+      </c>
+      <c r="G10" t="s">
+        <v>225</v>
+      </c>
+      <c r="H10" t="s">
+        <v>226</v>
+      </c>
+      <c r="I10" t="s">
+        <v>227</v>
+      </c>
+      <c r="L10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" t="s">
+        <v>20</v>
+      </c>
+      <c r="P10" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Test_Case.xlsx
+++ b/Test_Case.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Progress\OrangHRM\All_Documnets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8164878F-5EC5-450A-9ED1-B446D5C9C66D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B93FF55-6D3F-4C0C-A012-1161A1BB9084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
     <sheet name="PIM" sheetId="4" r:id="rId2"/>
+    <sheet name="Admin" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Login!$A$1:$P$28</definedName>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="303">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -804,13 +805,202 @@
   </si>
   <si>
     <t>FR-15, FR-16</t>
+  </si>
+  <si>
+    <t>TC-013-01</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Verify Admin menu is displayed after successful login</t>
+  </si>
+  <si>
+    <t>Verify Admin menu is visible after successful login</t>
+  </si>
+  <si>
+    <t>User is on the Login page</t>
+  </si>
+  <si>
+    <t>Valid Username, Valid Password</t>
+  </si>
+  <si>
+    <t>Dashboard is displayed and Admin menu is visible.</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Not Executed</t>
+  </si>
+  <si>
+    <t>Pallavi Devadiga</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>User is logged in</t>
+  </si>
+  <si>
+    <t>TC-014-01</t>
+  </si>
+  <si>
+    <t>Verify user is able to open the Admin module</t>
+  </si>
+  <si>
+    <t>Verify Admin page opens successfully</t>
+  </si>
+  <si>
+    <t>1. Login to OrangeHRM.2. Click the Admin menu.</t>
+  </si>
+  <si>
+    <t>Admin page is displayed successfully.</t>
+  </si>
+  <si>
+    <t>TC-014-02</t>
+  </si>
+  <si>
+    <t>Verify Admin page displays User Management section</t>
+  </si>
+  <si>
+    <t>User is on Admin page</t>
+  </si>
+  <si>
+    <t>1. Open Admin module.</t>
+  </si>
+  <si>
+    <t>User Management section is displayed.</t>
+  </si>
+  <si>
+    <t>TC-015-01</t>
+  </si>
+  <si>
+    <t>Verify Add User page is displayed when clicking the Add button</t>
+  </si>
+  <si>
+    <t>Verify Add button is available</t>
+  </si>
+  <si>
+    <t>Add button is displayed.</t>
+  </si>
+  <si>
+    <t>TC-015-02</t>
+  </si>
+  <si>
+    <t>Verify Add User page opens</t>
+  </si>
+  <si>
+    <t>1. Click Add button.</t>
+  </si>
+  <si>
+    <t>Add User page is displayed.</t>
+  </si>
+  <si>
+    <t>TC-015-03</t>
+  </si>
+  <si>
+    <t>Verify all required fields are displayed on Add User page</t>
+  </si>
+  <si>
+    <t>User is on Add User page</t>
+  </si>
+  <si>
+    <t>1. Open Add User page.2. Observe the form.</t>
+  </si>
+  <si>
+    <t>User Role, Employee Name, Status, Username, Password, Confirm Password, Save and Cancel buttons are displayed.</t>
+  </si>
+  <si>
+    <t>TC-016-01</t>
+  </si>
+  <si>
+    <t>Verify a new user can be added with valid details</t>
+  </si>
+  <si>
+    <t>Verify user creation with valid details</t>
+  </si>
+  <si>
+    <t>Valid User Role, Employee Name, Status, Username, Password</t>
+  </si>
+  <si>
+    <t>1. Fill all mandatory fields with valid data.2. Click Save.</t>
+  </si>
+  <si>
+    <t>New user is created successfully and success message is displayed.</t>
+  </si>
+  <si>
+    <t>TC-016-02</t>
+  </si>
+  <si>
+    <t>Verify newly created user appears in search results</t>
+  </si>
+  <si>
+    <t>User is created</t>
+  </si>
+  <si>
+    <t>Newly created Username</t>
+  </si>
+  <si>
+    <t>1. Search using the created username.</t>
+  </si>
+  <si>
+    <t>Newly created user is displayed in the search result.</t>
+  </si>
+  <si>
+    <t>TC-016-03</t>
+  </si>
+  <si>
+    <t>Verify Save button is enabled after entering valid details</t>
+  </si>
+  <si>
+    <t>Valid data</t>
+  </si>
+  <si>
+    <t>1. Enter all mandatory fields.2. Observe Save button.</t>
+  </si>
+  <si>
+    <t>Save button is enabled.</t>
+  </si>
+  <si>
+    <t>TC-016-04</t>
+  </si>
+  <si>
+    <t>Verify Cancel button navigates back to User List</t>
+  </si>
+  <si>
+    <t>1. Click Cancel.</t>
+  </si>
+  <si>
+    <t>User is redirected to the Admin User List page.</t>
+  </si>
+  <si>
+    <t>1. Open OrangeHRM.
+2. Enter valid username and password.
+3. Click Login.</t>
+  </si>
+  <si>
+    <t>verifyAdminMenuisDisplayed</t>
+  </si>
+  <si>
+    <t>verifyOpenAdminMenu</t>
+  </si>
+  <si>
+    <t>verifyUserManagemnetDisplayed</t>
+  </si>
+  <si>
+    <t>1. Open Admin module.
+2. Verify Add button.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -831,6 +1021,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -853,7 +1049,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -861,7 +1057,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1532,7 +1731,7 @@
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" t="s">
         <v>140</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -1544,7 +1743,7 @@
       <c r="H9" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" t="s">
         <v>145</v>
       </c>
       <c r="J9" s="2" t="s">
@@ -1576,7 +1775,7 @@
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" t="s">
         <v>141</v>
       </c>
       <c r="F10" s="2" t="s">
@@ -1588,7 +1787,7 @@
       <c r="H10" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" t="s">
         <v>145</v>
       </c>
       <c r="J10" s="2"/>
@@ -1618,7 +1817,7 @@
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" t="s">
         <v>164</v>
       </c>
       <c r="F11" s="2" t="s">
@@ -1662,7 +1861,7 @@
       <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" t="s">
         <v>165</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -1702,7 +1901,7 @@
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" t="s">
         <v>142</v>
       </c>
       <c r="F13" s="2" t="s">
@@ -1714,7 +1913,7 @@
       <c r="H13" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" t="s">
         <v>146</v>
       </c>
       <c r="J13" s="2" t="s">
@@ -1746,7 +1945,7 @@
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" t="s">
         <v>151</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -1758,7 +1957,7 @@
       <c r="H14" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" t="s">
         <v>149</v>
       </c>
       <c r="J14" s="2" t="s">
@@ -2109,7 +2308,7 @@
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="3" t="s">
+      <c r="P22" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2819,4 +3018,574 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE1513A-A660-4331-87EA-4B91EB5E2EEA}">
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.88671875" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" customWidth="1"/>
+    <col min="8" max="8" width="18.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>